--- a/generated/sources/reports/retail_controlling/weekly_flash/Flash_W41_2026.xlsx
+++ b/generated/sources/reports/retail_controlling/weekly_flash/Flash_W41_2026.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="210">
   <si>
-    <t>MONCLER  |  Retail Controlling</t>
+    <t>VALENTINO  |  Retail Controlling</t>
   </si>
   <si>
     <t>WEEKLY SALES FLASH - WEEK 41 / 2026</t>
@@ -64,7 +64,7 @@
     <t>- LON01: private client evening Thu 08/10.</t>
   </si>
   <si>
-    <t>- ILVARO powder pink sold out in Asia within days (celebrity effect), DC top-up landed 08/10.</t>
+    <t>- IRIDIA powder pink sold out in Asia within days (celebrity effect), DC top-up landed 08/10.</t>
   </si>
   <si>
     <t>- SIN01: F1 GP weekend 09-11/10.</t>
@@ -589,58 +589,58 @@
     <t>Units returned</t>
   </si>
   <si>
-    <t>MAYA</t>
+    <t>NOVA</t>
   </si>
   <si>
     <t>Outerwear</t>
   </si>
   <si>
-    <t>MAIRE</t>
-  </si>
-  <si>
-    <t>HERMINE</t>
-  </si>
-  <si>
-    <t>BADY</t>
-  </si>
-  <si>
-    <t>MONTCLA</t>
-  </si>
-  <si>
-    <t>ILVARO</t>
-  </si>
-  <si>
-    <t>TRICOT PADDED CARDIGAN</t>
+    <t>AUREA</t>
+  </si>
+  <si>
+    <t>LIVIANA</t>
+  </si>
+  <si>
+    <t>ARIA</t>
+  </si>
+  <si>
+    <t>MISTRAL</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>VLOGO PADDED CARDIGAN</t>
   </si>
   <si>
     <t>Knitwear</t>
   </si>
   <si>
-    <t>KARAKORUM</t>
-  </si>
-  <si>
-    <t>FLAMMETTE</t>
-  </si>
-  <si>
-    <t>MONTGENEVRE</t>
-  </si>
-  <si>
-    <t>LOGO CARDIGAN</t>
-  </si>
-  <si>
-    <t>ROSIERE</t>
-  </si>
-  <si>
-    <t>LOGO HOODIE</t>
+    <t>COSIMO</t>
+  </si>
+  <si>
+    <t>FIAMMETTA</t>
+  </si>
+  <si>
+    <t>MONTELUCE</t>
+  </si>
+  <si>
+    <t>VLOGO CARDIGAN</t>
+  </si>
+  <si>
+    <t>RIVIERA</t>
+  </si>
+  <si>
+    <t>VLOGO HOODIE</t>
   </si>
   <si>
     <t>Jersey</t>
   </si>
   <si>
-    <t>AMBRINE</t>
-  </si>
-  <si>
-    <t>POLARIS CAPE</t>
+    <t>AMALIA</t>
+  </si>
+  <si>
+    <t>ASTRA CAPE</t>
   </si>
   <si>
     <t>Exchange rates used (local currency per 1 EUR)</t>
